--- a/metadata/Plate4/SRKW_Diet_Plate4_MetaData.xlsx
+++ b/metadata/Plate4/SRKW_Diet_Plate4_MetaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/mball3_uw_edu/Documents/Documents/WADE LAB/SRKW/metadata/Plate4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FEBAD8-4CC0-0C41-948B-8F93DE963753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{311AC791-85DB-1843-8E97-EE739A8A2EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21975" yWindow="1275" windowWidth="21600" windowHeight="11295" xr2:uid="{518B7A33-C5FE-E642-B8D5-47A99A98280E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{518B7A33-C5FE-E642-B8D5-47A99A98280E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="115">
   <si>
     <t>Sample_name</t>
   </si>
@@ -372,13 +372,22 @@
   </si>
   <si>
     <t>NEG</t>
+  </si>
+  <si>
+    <t>K37</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>J42</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -388,6 +397,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -413,11 +429,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -753,12 +770,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0E5F67-981F-2842-8BC9-09C804A53EC3}">
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="2" max="2" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.8125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -778,7 +795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -798,7 +815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -818,7 +835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -838,7 +855,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -858,7 +875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -878,7 +895,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -898,7 +915,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -918,7 +935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -938,7 +955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -958,7 +975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>10</v>
       </c>
@@ -978,7 +995,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>11</v>
       </c>
@@ -998,7 +1015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1018,13 +1035,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
       </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="D14">
         <v>2011</v>
       </c>
@@ -1035,13 +1055,16 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>46</v>
       </c>
+      <c r="C15" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="D15">
         <v>2011</v>
       </c>
@@ -1052,7 +1075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1069,13 +1092,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>48</v>
       </c>
+      <c r="C17" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="D17">
         <v>2011</v>
       </c>
@@ -1086,7 +1112,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1106,7 +1132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1126,7 +1152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1146,7 +1172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1166,7 +1192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1186,7 +1212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1206,7 +1232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1226,7 +1252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1246,7 +1272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1266,7 +1292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1286,7 +1312,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1306,7 +1332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1326,7 +1352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1346,7 +1372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1366,7 +1392,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1386,7 +1412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1406,7 +1432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1426,7 +1452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1446,7 +1472,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1466,7 +1492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1486,7 +1512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1506,7 +1532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1526,7 +1552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1546,7 +1572,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1563,13 +1589,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>73</v>
       </c>
+      <c r="C42" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="D42">
         <v>2012</v>
       </c>
@@ -1580,7 +1609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1600,7 +1629,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1620,7 +1649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1640,7 +1669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1660,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1680,7 +1709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1700,7 +1729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1720,7 +1749,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1740,7 +1769,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1760,7 +1789,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1780,7 +1809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1800,7 +1829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1820,7 +1849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1840,7 +1869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1860,7 +1889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1880,7 +1909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1900,7 +1929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1920,7 +1949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1940,7 +1969,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1960,7 +1989,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1980,7 +2009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2000,7 +2029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2020,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2040,10 +2069,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.5">
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.5">
       <c r="D70" s="1"/>
     </row>
   </sheetData>
